--- a/11-Dashboards/dashboard-testcases.xlsx
+++ b/11-Dashboards/dashboard-testcases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="222">
   <si>
     <t>META</t>
   </si>
@@ -599,6 +599,84 @@
   </si>
   <si>
     <t>[รอ Q7,Q9] การ์ด Total +1 (=7) และ New +1 (=2) หลัง reload (ตามข้อเสนอ: อัปเดตเมื่อ reload)</t>
+  </si>
+  <si>
+    <t>TA-03</t>
+  </si>
+  <si>
+    <t>Case Dashboard period toggle Monthly/Daily</t>
+  </si>
+  <si>
+    <t>CD8</t>
+  </si>
+  <si>
+    <t>มีบัญชี Supervisor login STG แล้ว · Case Dashboard เข้าผ่านเมนู Cases → Case Dashboard (/cms/) · ตรวจสอบว่า V2.0 deploy บน STG แล้ว · default view = Monthly</t>
+  </si>
+  <si>
+    <t>TA-03_TC-01</t>
+  </si>
+  <si>
+    <t>เปลี่ยนจาก Monthly เป็น Daily view</t>
+  </si>
+  <si>
+    <t>1. กดปุ่มหรือ dropdown เปลี่ยนช่วงเวลาเป็น Daily บน Case Dashboard</t>
+  </si>
+  <si>
+    <t>[รอ V2.0 deploy] chart/data เปลี่ยนเป็น daily breakdown (แสดงข้อมูลรายวัน ไม่ใช่รายเดือน)</t>
+  </si>
+  <si>
+    <t>มีบัญชี Supervisor login STG แล้ว · Case Dashboard เข้าผ่านเมนู Cases → Case Dashboard (/cms/) · อยู่ใน Daily view</t>
+  </si>
+  <si>
+    <t>TA-03_TC-02</t>
+  </si>
+  <si>
+    <t>เปลี่ยนกลับจาก Daily เป็น Monthly view</t>
+  </si>
+  <si>
+    <t>1. กดปุ่มหรือ dropdown เปลี่ยนกลับเป็น Monthly</t>
+  </si>
+  <si>
+    <t>[รอ V2.0 deploy] chart กลับเป็น stacked bar รายเดือน (เช่น Jan–Jun 2026) ไม่ error ไม่ค้าง</t>
+  </si>
+  <si>
+    <t>TA-04</t>
+  </si>
+  <si>
+    <t>Case Dashboard exported data (V2.0)</t>
+  </si>
+  <si>
+    <t>CD9</t>
+  </si>
+  <si>
+    <t>มีบัญชี Supervisor login STG แล้ว · Case Dashboard เข้าผ่านเมนู Cases → Case Dashboard (/cms/) · ตรวจสอบว่า V2.0 deploy บน STG แล้ว</t>
+  </si>
+  <si>
+    <t>TA-04_TC-01</t>
+  </si>
+  <si>
+    <t>Export Case Dashboard report → ดาวน์โหลดได้</t>
+  </si>
+  <si>
+    <t>1. กดปุ่ม Export บน Case Dashboard</t>
+  </si>
+  <si>
+    <t>[รอ Q2, V2.0 deploy] ระบบสร้างไฟล์รายงาน (format ตาม Q2 เช่น .xlsx) ดาวน์โหลดได้ ไฟล์ไม่ว่าง</t>
+  </si>
+  <si>
+    <t>มีบัญชี Supervisor login STG แล้ว · Case Dashboard เข้าผ่านเมนู Cases → Case Dashboard (/cms/) · จับเวลา start จากกด Export</t>
+  </si>
+  <si>
+    <t>TA-04_TC-02</t>
+  </si>
+  <si>
+    <t>Export เสร็จภายใน 60 วินาที (BRD target)</t>
+  </si>
+  <si>
+    <t>1. กดปุ่ม Export บน Case Dashboard แล้วจับเวลาจนดาวน์โหลดเสร็จ</t>
+  </si>
+  <si>
+    <t>[รอ Q2, V2.0 deploy] เวลา generate &lt; 60 วินาที (BRD FR-07 §3.5.7 Report Generation &lt; 1 min)</t>
   </si>
 </sst>
 </file>
@@ -975,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="12" customWidth="1"/>
@@ -3052,6 +3130,290 @@
         <v>45</v>
       </c>
     </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" t="s">
+        <v>198</v>
+      </c>
+      <c r="G30" t="s">
+        <v>199</v>
+      </c>
+      <c r="H30" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" t="s">
+        <v>201</v>
+      </c>
+      <c r="J30" t="s">
+        <v>40</v>
+      </c>
+      <c r="K30" t="s">
+        <v>41</v>
+      </c>
+      <c r="L30" t="s">
+        <v>202</v>
+      </c>
+      <c r="M30" t="s">
+        <v>50</v>
+      </c>
+      <c r="N30" t="s">
+        <v>203</v>
+      </c>
+      <c r="O30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P30" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>45</v>
+      </c>
+      <c r="R30" t="s">
+        <v>45</v>
+      </c>
+      <c r="S30" t="s">
+        <v>45</v>
+      </c>
+      <c r="T30" t="s">
+        <v>45</v>
+      </c>
+      <c r="U30" t="s">
+        <v>45</v>
+      </c>
+      <c r="V30" t="s">
+        <v>45</v>
+      </c>
+      <c r="W30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" t="s">
+        <v>196</v>
+      </c>
+      <c r="E31" t="s">
+        <v>197</v>
+      </c>
+      <c r="F31" t="s">
+        <v>198</v>
+      </c>
+      <c r="G31" t="s">
+        <v>204</v>
+      </c>
+      <c r="H31" t="s">
+        <v>205</v>
+      </c>
+      <c r="I31" t="s">
+        <v>206</v>
+      </c>
+      <c r="J31" t="s">
+        <v>40</v>
+      </c>
+      <c r="K31" t="s">
+        <v>41</v>
+      </c>
+      <c r="L31" t="s">
+        <v>207</v>
+      </c>
+      <c r="M31" t="s">
+        <v>50</v>
+      </c>
+      <c r="N31" t="s">
+        <v>208</v>
+      </c>
+      <c r="O31" t="s">
+        <v>45</v>
+      </c>
+      <c r="P31" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>45</v>
+      </c>
+      <c r="R31" t="s">
+        <v>45</v>
+      </c>
+      <c r="S31" t="s">
+        <v>45</v>
+      </c>
+      <c r="T31" t="s">
+        <v>45</v>
+      </c>
+      <c r="U31" t="s">
+        <v>45</v>
+      </c>
+      <c r="V31" t="s">
+        <v>45</v>
+      </c>
+      <c r="W31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" t="s">
+        <v>209</v>
+      </c>
+      <c r="E32" t="s">
+        <v>210</v>
+      </c>
+      <c r="F32" t="s">
+        <v>211</v>
+      </c>
+      <c r="G32" t="s">
+        <v>212</v>
+      </c>
+      <c r="H32" t="s">
+        <v>213</v>
+      </c>
+      <c r="I32" t="s">
+        <v>214</v>
+      </c>
+      <c r="J32" t="s">
+        <v>40</v>
+      </c>
+      <c r="K32" t="s">
+        <v>41</v>
+      </c>
+      <c r="L32" t="s">
+        <v>215</v>
+      </c>
+      <c r="M32" t="s">
+        <v>50</v>
+      </c>
+      <c r="N32" t="s">
+        <v>216</v>
+      </c>
+      <c r="O32" t="s">
+        <v>45</v>
+      </c>
+      <c r="P32" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>45</v>
+      </c>
+      <c r="R32" t="s">
+        <v>45</v>
+      </c>
+      <c r="S32" t="s">
+        <v>45</v>
+      </c>
+      <c r="T32" t="s">
+        <v>45</v>
+      </c>
+      <c r="U32" t="s">
+        <v>45</v>
+      </c>
+      <c r="V32" t="s">
+        <v>45</v>
+      </c>
+      <c r="W32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E33" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" t="s">
+        <v>211</v>
+      </c>
+      <c r="G33" t="s">
+        <v>217</v>
+      </c>
+      <c r="H33" t="s">
+        <v>218</v>
+      </c>
+      <c r="I33" t="s">
+        <v>219</v>
+      </c>
+      <c r="J33" t="s">
+        <v>40</v>
+      </c>
+      <c r="K33" t="s">
+        <v>41</v>
+      </c>
+      <c r="L33" t="s">
+        <v>220</v>
+      </c>
+      <c r="M33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N33" t="s">
+        <v>221</v>
+      </c>
+      <c r="O33" t="s">
+        <v>45</v>
+      </c>
+      <c r="P33" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>45</v>
+      </c>
+      <c r="R33" t="s">
+        <v>45</v>
+      </c>
+      <c r="S33" t="s">
+        <v>45</v>
+      </c>
+      <c r="T33" t="s">
+        <v>45</v>
+      </c>
+      <c r="U33" t="s">
+        <v>45</v>
+      </c>
+      <c r="V33" t="s">
+        <v>45</v>
+      </c>
+      <c r="W33" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
